--- a/public/exports-from-60/29189803.xlsx
+++ b/public/exports-from-60/29189803.xlsx
@@ -25714,12 +25714,12 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041324</t>
+          <t xml:space="preserve">311041311</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -26104,12 +26104,12 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -26539,7 +26539,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319330</t>
+          <t xml:space="preserve">311319327</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442081</t>
+          <t xml:space="preserve">311442101</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624659</t>
+          <t xml:space="preserve">311624658</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -41164,7 +41164,7 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -41239,7 +41239,7 @@
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
@@ -41314,7 +41314,7 @@
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759943</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
